--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -2528,7 +2528,7 @@
         <v>135762156</v>
       </c>
       <c r="B17" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135779481</v>
       </c>
       <c r="B21" t="n">
-        <v>56866</v>
+        <v>56867</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>135779311</v>
       </c>
       <c r="B22" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>135779178</v>
       </c>
       <c r="B23" t="n">
-        <v>56868</v>
+        <v>56869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -2528,7 +2528,7 @@
         <v>135762156</v>
       </c>
       <c r="B17" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135779481</v>
       </c>
       <c r="B21" t="n">
-        <v>56867</v>
+        <v>56872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>135779311</v>
       </c>
       <c r="B22" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>135779178</v>
       </c>
       <c r="B23" t="n">
-        <v>56869</v>
+        <v>56874</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 2048-2026 artfynd.xlsx
+++ b/artfynd/S 2048-2026 artfynd.xlsx
@@ -2528,7 +2528,7 @@
         <v>135762156</v>
       </c>
       <c r="B17" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
